--- a/rosnedra_forecast/2026/rosnedra_page13.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page13.xlsx
@@ -416,12 +416,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -443,214 +443,239 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
+          <t>Извлекаемые запасы и прогнозные ресурсы</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Южно-Тамбейский</t>
+          <t>Южно-Урманный</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 132,4 млрд м3
-конденсат (извл.)
-C1 - 7,8 млн т</t>
+          <t>нефть (извл.)
+Д0 - 1.625 млн.т.
+Д1 - 1.4 млн.т
+Д2 - 0.1 млн.т</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Северо-Тамбейский</t>
+          <t>Южно-Ялотский</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 118,9 млрд м3
-конденсат (извл.)
-C1 - 6,9 млн т</t>
+          <t>нефть (извл.):
+Д1 - 16,1 млн. т
+Д2 - 0,9 млн. т
+газ (изв.):
+Д2 - 1,1 млрд. м3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Западно-Сеяхинский</t>
+          <t>Юильский 6</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 94,5 млрд м3
-конденсат (извл.)
-C1 - 5,1 млн т</t>
+          <t>нефть (извл.):
+Д1 - 1,2 млн. т
+Д2 - 3,2 млн. т
+газ (извл.):
+Д2 - 3,0 млрд. м3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Восточно-Сеяхинский</t>
+          <t>Юильский 7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 88,7 млрд м3
-конденсат (извл.)
-C1 - 4,8 млн т</t>
+          <t>нефть (извл)
+Д1 - 1,2 млн.т
+Д2 - 3,0 млн.т
+газ
+Д2 - 3,0 млрд.м3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Салмановский</t>
+          <t>Юильский 8</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.)
-C1 - 24,6 млн т
-газ (извл.)
-C1 - 62,3 млрд м3
-конденсат (извл.)
-C1 - 3,4 млн т</t>
+          <t>нефть (извл)
+Д1 - 2,0 млн.т
+Д2 - 5.0 млн.т
+газ
+Д2 - 2,0 млрд.м3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Утренний</t>
+          <t>Юильский 14</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 198,4 млрд м3
-конденсат (извл.)
-C1 - 12,6 млн т</t>
+          <t>нефть (извл)
+Д1 - 2,0млн.т
+Д2 - 5,0 млн.т
+газ
+Д2 - 2,0 млрд.м3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Геофизический</t>
+          <t>Юильский 15</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 76,8 млрд м3</t>
+          <t>нефть (извл)
+Д1 - 28,0 млн.т.
+Д2 -1,4 млн.т.
+газ
+Д2 2,2 млрд.м3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Чувашская Республика</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Арктический</t>
+          <t>Ибресинский</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>газ (извл.)
-C1 - 154,1 млрд м3
-конденсат (извл.)
-C1 - 8,3 млн т</t>
+          <t>нефть (геол./извл.):
+D1-0,99/0,168 млн.т
+D2 - 1,712/0,357 млн.т;</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>Чувашская Республика</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Турмышский</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>нефть (геол./извл.):
+D1-1,444/0,245 млн.т
+D2 - 2,497/0,520 млн.т;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
           <t>Ямало-Ненецкий автономный округ</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Нурминский</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-C1 - 9,2 млн т
-газ (извл.)
-C1 - 14,7 млрд м3</t>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Вынгаяхинский (пласты кровля ПК9/2 – кровля БП11)</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>газ (извл.):
+B1 - 0,522 млрд.м3;</t>
         </is>
       </c>
     </row>
